--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260602.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>31,081,615</t>
+          <t>26,782,289</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>26,782,289</t>
+          <t>31,081,615</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>38,889,705</t>
+          <t>6,891,931</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>6,891,931</t>
+          <t>38,889,705</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>316,253,492</t>
+          <t>1,921,630</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,921,630</t>
+          <t>316,253,492</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>21,775,770</t>
+          <t>1,687,227</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,687,227</t>
+          <t>21,775,770</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>19,298,811</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>19,298,811</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
